--- a/templates/pricing-template.xlsx
+++ b/templates/pricing-template.xlsx
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,6 +118,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,7 +515,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>نموذج أسعار التمر المجدول الأردني — الأصناف الأربعة × الأحجام الستة (املأ خانات الأسعار فقط)</t>
+          <t>نموذج أسعار التمر المجدول الأردني — بالدينار الأردني (املأ خانات الدينار فقط؛ يُحسب الدولار تلقائياً)</t>
         </is>
       </c>
     </row>
@@ -564,22 +572,22 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>FOB (JOD)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>FOB (USD)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>FOB (JOD)</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>تجزئة (JOD)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>تجزئة (USD)</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>تجزئة (JOD)</t>
         </is>
       </c>
     </row>
@@ -635,75 +643,75 @@
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4">
-        <f>IF(K3="","",ROUND(K3*0.709,2))</f>
+      <c r="L3" s="5">
+        <f>IF(K3="","",ROUND(K3/0.709,2))</f>
         <v/>
       </c>
       <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4">
-        <f>IF(M3="","",ROUND(M3*0.709,2))</f>
+      <c r="N3" s="5">
+        <f>IF(M3="","",ROUND(M3/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>بريميوم</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>جامبو</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Jumbo</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>22.0 – 24.9 غ</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>41 – 45</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>4.5 – 5.5 سم</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>0 – 10 %</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4">
-        <f>IF(K4="","",ROUND(K4*0.709,2))</f>
+      <c r="L4" s="5">
+        <f>IF(K4="","",ROUND(K4/0.709,2))</f>
         <v/>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4">
-        <f>IF(M4="","",ROUND(M4*0.709,2))</f>
+      <c r="N4" s="5">
+        <f>IF(M4="","",ROUND(M4/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -759,75 +767,75 @@
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4">
-        <f>IF(K5="","",ROUND(K5*0.709,2))</f>
+      <c r="L5" s="5">
+        <f>IF(K5="","",ROUND(K5/0.709,2))</f>
         <v/>
       </c>
       <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4">
-        <f>IF(M5="","",ROUND(M5*0.709,2))</f>
+      <c r="N5" s="5">
+        <f>IF(M5="","",ROUND(M5/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>بريميوم</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>ميديوم</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>14.0 – 16.9 غ</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>60 – 71</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>3.5 – 4.5 سم</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>0 – 10 %</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4">
-        <f>IF(K6="","",ROUND(K6*0.709,2))</f>
+      <c r="L6" s="5">
+        <f>IF(K6="","",ROUND(K6/0.709,2))</f>
         <v/>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4">
-        <f>IF(M6="","",ROUND(M6*0.709,2))</f>
+      <c r="N6" s="5">
+        <f>IF(M6="","",ROUND(M6/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -883,75 +891,75 @@
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4">
-        <f>IF(K7="","",ROUND(K7*0.709,2))</f>
+      <c r="L7" s="5">
+        <f>IF(K7="","",ROUND(K7/0.709,2))</f>
         <v/>
       </c>
       <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4">
-        <f>IF(M7="","",ROUND(M7*0.709,2))</f>
+      <c r="N7" s="5">
+        <f>IF(M7="","",ROUND(M7/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>بريميوم</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>بيبي سمول</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Baby Small</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>7 – 10 غ</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>100 – 140</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>2.5 – 3.0 سم</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>0 – 10 %</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4">
-        <f>IF(K8="","",ROUND(K8*0.709,2))</f>
+      <c r="L8" s="5">
+        <f>IF(K8="","",ROUND(K8/0.709,2))</f>
         <v/>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4">
-        <f>IF(M8="","",ROUND(M8*0.709,2))</f>
+      <c r="N8" s="5">
+        <f>IF(M8="","",ROUND(M8/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1007,75 +1015,75 @@
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4">
-        <f>IF(K9="","",ROUND(K9*0.709,2))</f>
+      <c r="L9" s="5">
+        <f>IF(K9="","",ROUND(K9/0.709,2))</f>
         <v/>
       </c>
       <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4">
-        <f>IF(M9="","",ROUND(M9*0.709,2))</f>
+      <c r="N9" s="5">
+        <f>IF(M9="","",ROUND(M9/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ديلايت</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Delight</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>DL</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>جامبو</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Jumbo</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>22.0 – 24.9 غ</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>41 – 45</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>4.5 – 5.5 سم</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>10 – 20 %</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4">
-        <f>IF(K10="","",ROUND(K10*0.709,2))</f>
+      <c r="L10" s="5">
+        <f>IF(K10="","",ROUND(K10/0.709,2))</f>
         <v/>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4">
-        <f>IF(M10="","",ROUND(M10*0.709,2))</f>
+      <c r="N10" s="5">
+        <f>IF(M10="","",ROUND(M10/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1131,75 +1139,75 @@
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4">
-        <f>IF(K11="","",ROUND(K11*0.709,2))</f>
+      <c r="L11" s="5">
+        <f>IF(K11="","",ROUND(K11/0.709,2))</f>
         <v/>
       </c>
       <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4">
-        <f>IF(M11="","",ROUND(M11*0.709,2))</f>
+      <c r="N11" s="5">
+        <f>IF(M11="","",ROUND(M11/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ديلايت</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Delight</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>DL</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>ميديوم</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>14.0 – 16.9 غ</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>60 – 71</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>3.5 – 4.5 سم</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>10 – 20 %</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4">
-        <f>IF(K12="","",ROUND(K12*0.709,2))</f>
+      <c r="L12" s="5">
+        <f>IF(K12="","",ROUND(K12/0.709,2))</f>
         <v/>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4">
-        <f>IF(M12="","",ROUND(M12*0.709,2))</f>
+      <c r="N12" s="5">
+        <f>IF(M12="","",ROUND(M12/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1255,75 +1263,75 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4">
-        <f>IF(K13="","",ROUND(K13*0.709,2))</f>
+      <c r="L13" s="5">
+        <f>IF(K13="","",ROUND(K13/0.709,2))</f>
         <v/>
       </c>
       <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4">
-        <f>IF(M13="","",ROUND(M13*0.709,2))</f>
+      <c r="N13" s="5">
+        <f>IF(M13="","",ROUND(M13/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ديلايت</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Delight</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>DL</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>بيبي سمول</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Baby Small</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>7 – 10 غ</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>100 – 140</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>2.5 – 3.0 سم</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>10 – 20 %</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4">
-        <f>IF(K14="","",ROUND(K14*0.709,2))</f>
+      <c r="L14" s="5">
+        <f>IF(K14="","",ROUND(K14/0.709,2))</f>
         <v/>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4">
-        <f>IF(M14="","",ROUND(M14*0.709,2))</f>
+      <c r="N14" s="5">
+        <f>IF(M14="","",ROUND(M14/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1379,75 +1387,75 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4">
-        <f>IF(K15="","",ROUND(K15*0.709,2))</f>
+      <c r="L15" s="5">
+        <f>IF(K15="","",ROUND(K15/0.709,2))</f>
         <v/>
       </c>
       <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4">
-        <f>IF(M15="","",ROUND(M15*0.709,2))</f>
+      <c r="N15" s="5">
+        <f>IF(M15="","",ROUND(M15/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>كلاسيك</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Classic</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>جامبو</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Jumbo</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>22.0 – 24.9 غ</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>41 – 45</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>4.5 – 5.5 سم</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>20 – 30 %</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4">
-        <f>IF(K16="","",ROUND(K16*0.709,2))</f>
+      <c r="L16" s="5">
+        <f>IF(K16="","",ROUND(K16/0.709,2))</f>
         <v/>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4">
-        <f>IF(M16="","",ROUND(M16*0.709,2))</f>
+      <c r="N16" s="5">
+        <f>IF(M16="","",ROUND(M16/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1503,75 +1511,75 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4">
-        <f>IF(K17="","",ROUND(K17*0.709,2))</f>
+      <c r="L17" s="5">
+        <f>IF(K17="","",ROUND(K17/0.709,2))</f>
         <v/>
       </c>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4">
-        <f>IF(M17="","",ROUND(M17*0.709,2))</f>
+      <c r="N17" s="5">
+        <f>IF(M17="","",ROUND(M17/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>كلاسيك</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Classic</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>ميديوم</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>14.0 – 16.9 غ</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>60 – 71</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>3.5 – 4.5 سم</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>20 – 30 %</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4">
-        <f>IF(K18="","",ROUND(K18*0.709,2))</f>
+      <c r="L18" s="5">
+        <f>IF(K18="","",ROUND(K18/0.709,2))</f>
         <v/>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4">
-        <f>IF(M18="","",ROUND(M18*0.709,2))</f>
+      <c r="N18" s="5">
+        <f>IF(M18="","",ROUND(M18/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1627,75 +1635,75 @@
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4">
-        <f>IF(K19="","",ROUND(K19*0.709,2))</f>
+      <c r="L19" s="5">
+        <f>IF(K19="","",ROUND(K19/0.709,2))</f>
         <v/>
       </c>
       <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4">
-        <f>IF(M19="","",ROUND(M19*0.709,2))</f>
+      <c r="N19" s="5">
+        <f>IF(M19="","",ROUND(M19/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>كلاسيك</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Classic</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>بيبي سمول</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Baby Small</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>7 – 10 غ</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>100 – 140</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>2.5 – 3.0 سم</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>20 – 30 %</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4">
-        <f>IF(K20="","",ROUND(K20*0.709,2))</f>
+      <c r="L20" s="5">
+        <f>IF(K20="","",ROUND(K20/0.709,2))</f>
         <v/>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4">
-        <f>IF(M20="","",ROUND(M20*0.709,2))</f>
+      <c r="N20" s="5">
+        <f>IF(M20="","",ROUND(M20/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1751,75 +1759,75 @@
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4">
-        <f>IF(K21="","",ROUND(K21*0.709,2))</f>
+      <c r="L21" s="5">
+        <f>IF(K21="","",ROUND(K21/0.709,2))</f>
         <v/>
       </c>
       <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4">
-        <f>IF(M21="","",ROUND(M21*0.709,2))</f>
+      <c r="N21" s="5">
+        <f>IF(M21="","",ROUND(M21/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ستاندرد</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>جامبو</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Jumbo</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>22.0 – 24.9 غ</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>41 – 45</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>4.5 – 5.5 سم</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>أكثر من 30 %</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4">
-        <f>IF(K22="","",ROUND(K22*0.709,2))</f>
+      <c r="L22" s="5">
+        <f>IF(K22="","",ROUND(K22/0.709,2))</f>
         <v/>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4">
-        <f>IF(M22="","",ROUND(M22*0.709,2))</f>
+      <c r="N22" s="5">
+        <f>IF(M22="","",ROUND(M22/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1875,75 +1883,75 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4">
-        <f>IF(K23="","",ROUND(K23*0.709,2))</f>
+      <c r="L23" s="5">
+        <f>IF(K23="","",ROUND(K23/0.709,2))</f>
         <v/>
       </c>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4">
-        <f>IF(M23="","",ROUND(M23*0.709,2))</f>
+      <c r="N23" s="5">
+        <f>IF(M23="","",ROUND(M23/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ستاندرد</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>ميديوم</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>14.0 – 16.9 غ</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>60 – 71</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>3.5 – 4.5 سم</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>أكثر من 30 %</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4">
-        <f>IF(K24="","",ROUND(K24*0.709,2))</f>
+      <c r="L24" s="5">
+        <f>IF(K24="","",ROUND(K24/0.709,2))</f>
         <v/>
       </c>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4">
-        <f>IF(M24="","",ROUND(M24*0.709,2))</f>
+      <c r="N24" s="5">
+        <f>IF(M24="","",ROUND(M24/0.709,2))</f>
         <v/>
       </c>
     </row>
@@ -1999,82 +2007,82 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4">
-        <f>IF(K25="","",ROUND(K25*0.709,2))</f>
+      <c r="L25" s="5">
+        <f>IF(K25="","",ROUND(K25/0.709,2))</f>
         <v/>
       </c>
       <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4">
-        <f>IF(M25="","",ROUND(M25*0.709,2))</f>
+      <c r="N25" s="5">
+        <f>IF(M25="","",ROUND(M25/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>ستاندرد</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>بيبي سمول</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Baby Small</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>7 – 10 غ</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>100 – 140</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>2.5 – 3.0 سم</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>أكثر من 30 %</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4">
-        <f>IF(K26="","",ROUND(K26*0.709,2))</f>
+      <c r="L26" s="5">
+        <f>IF(K26="","",ROUND(K26/0.709,2))</f>
         <v/>
       </c>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4">
-        <f>IF(M26="","",ROUND(M26*0.709,2))</f>
+      <c r="N26" s="5">
+        <f>IF(M26="","",ROUND(M26/0.709,2))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>ملاحظة: اكتب الأسعار بالدولار (FOB وتجزئة). يُحسب الدينار تلقائياً = الدولار × 0.709. اترك خانات الدينار فارغة إذا رغبت بالحساب التلقائي، أو اكتب قيمتك مباشرةً للتجاوز.</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>ملاحظة: اكتب الأسعار بالدينار الأردني (FOB JOD وتجزئة JOD). يُحسب الدولار تلقائياً = الدينار ÷ 0.709 (× 1.4104). اترك خانات الدولار فارغة للحساب التلقائي، أو اكتب قيمتك مباشرةً. عند الإرجاع سأعتمد الدينار وأحسب الدولار.</t>
         </is>
       </c>
     </row>
@@ -2096,55 +2104,55 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>تعليمات تعبئة النموذج:</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>تعليمات تعبئة النموذج (بالدينار الأردني):</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>1) العمود K (FOB USD) والعمود M (تجزئة USD): اكتب السعر بالدولار الأمريكي.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>1) العمود K (FOB JOD) والعمود M (تجزئة JOD): اكتب السعر بالدينار الأردني.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2) العمود L (FOB JOD) والعمود N (تجزئة JOD): يُحسبان تلقائياً = الدولار × 0.709.</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2) العمود L (FOB USD) والعمود N (تجزئة USD): يُحسبان تلقائياً = الدينار ÷ 0.709 (× 1.4104).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   يمكنك تركهما فارغين للحساب التلقائي، أو كتابة قيمة الدينار مباشرةً لتجاوز الحساب.</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   يمكنك تركهما فارغين للحساب التلقائي، أو كتابة قيمة الدولار مباشرةً لتجاوز الحساب.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>3) الأعمدة A–J (الدرجة، الحجم، الوزن، العدد، الطول، انفصال القشرة) ثابتة ولا تُعدّل.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>4) الأصناف: بريميوم / ديلايت / كلاسيك / ستاندرد. الأحجام: سوبر جامبو/جامبو/لارج/ميديوم/سمول/بيبي سمول.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>5) بعد التعبئة احفظ الملف وأعده ليتم اعتماد الأسعار في الموقع.</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>5) بعد التعبئة احفظ الملف وأعده ليتم اعتماد الأسعار بالدينار وحساب الدولار في الموقع.</t>
         </is>
       </c>
     </row>

--- a/templates/pricing-template.xlsx
+++ b/templates/pricing-template.xlsx
@@ -2101,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2156,20 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>6) FOB (Free On Board): سعر التصدير/الجملة عند ميناء الشحن قبل النقل الدولي — للكميات التجارية الكبيرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>7) تجزئة: السعر النهائي الذي يدفعه المستهلك النهائي في المتاجر ونقاط البيع.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
